--- a/rule_review/templates/规则验证空白.xlsx
+++ b/rule_review/templates/规则验证空白.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="1" r:id="R07d064d6a44e4371"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务事实" sheetId="2" r:id="R2a6851ca54064b9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则台账" sheetId="3" r:id="R159f1895283443f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则条件" sheetId="4" r:id="R10253dc6554242f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对照用例" sheetId="5" r:id="R7a5f20ae3eca484c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="1" r:id="Ra298f32bd0274a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务事实" sheetId="2" r:id="R224cda61aca045c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则台账" sheetId="3" r:id="Rb211b70dc20c41da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则条件" sheetId="4" r:id="Rb63ca915dbd84e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对照用例" sheetId="5" r:id="R6dcdb0a726bd4ca3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,12 +36,17 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF243B55"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -61,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,6 +85,15 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1329,6 +1343,7 @@
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1344,72 +1359,86 @@
       <x:c r="D1" s="5" t="str">
         <x:v>预期规则状态</x:v>
       </x:c>
+      <x:c r="E1" s="10" t="str">
+        <x:v>预期需求结论</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
       <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
       <x:c r="A3" s="2"/>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
       <x:c r="D3" s="2"/>
+      <x:c r="E3" s="2"/>
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
       <x:c r="A4" s="2"/>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="2"/>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
       <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="2"/>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
       <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="2"/>
       <x:c r="B7" s="2"/>
       <x:c r="C7" s="2"/>
       <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="2"/>
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
       <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="2"/>
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2"/>
       <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="2"/>
       <x:c r="B10" s="2"/>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="2"/>
       <x:c r="B11" s="2"/>
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="2"/>
       <x:c r="B12" s="2"/>
       <x:c r="C12" s="2"/>
       <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
